--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.3913089925374</v>
+        <v>9.001087711287328</v>
       </c>
       <c r="D2" t="n">
-        <v>57.14764816876842</v>
+        <v>9.286492827424869</v>
       </c>
       <c r="E2" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F2" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.66031690032489</v>
+        <v>6.932301496302795</v>
       </c>
       <c r="D3" t="n">
-        <v>43.6885911367323</v>
+        <v>7.099396059718999</v>
       </c>
       <c r="E3" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F3" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.35247874512098</v>
+        <v>6.557277796082158</v>
       </c>
       <c r="D4" t="n">
-        <v>18.965632146064</v>
+        <v>3.0819152237354</v>
       </c>
       <c r="E4" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F4" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48665766822528</v>
+        <v>6.904081871086608</v>
       </c>
       <c r="D5" t="n">
-        <v>7.858055664807859</v>
+        <v>1.276934045531277</v>
       </c>
       <c r="E5" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F5" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.23801872095833</v>
+        <v>5.726178042155729</v>
       </c>
       <c r="D6" t="n">
-        <v>10.36817432488568</v>
+        <v>1.684828327793924</v>
       </c>
       <c r="E6" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F6" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.83187676071962</v>
+        <v>8.422679973616939</v>
       </c>
       <c r="D7" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="E7" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F7" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>53.79890441055347</v>
+        <v>8.74232196671494</v>
       </c>
       <c r="D8" t="n">
-        <v>12.10436388250122</v>
+        <v>1.966959130906448</v>
       </c>
       <c r="E8" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F8" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>67.05660057269635</v>
+        <v>10.89669759306316</v>
       </c>
       <c r="D9" t="n">
-        <v>12.73507770585586</v>
+        <v>2.069450127201577</v>
       </c>
       <c r="E9" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F9" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.48445089992678</v>
+        <v>6.091223271238102</v>
       </c>
       <c r="D10" t="n">
-        <v>35.97364550140941</v>
+        <v>5.845717393979029</v>
       </c>
       <c r="E10" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F10" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.72850526427577</v>
+        <v>8.243382105444814</v>
       </c>
       <c r="D11" t="n">
-        <v>43.41801348675784</v>
+        <v>7.05542719159815</v>
       </c>
       <c r="E11" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F11" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>74.35373567643195</v>
+        <v>12.08248204742019</v>
       </c>
       <c r="D12" t="n">
-        <v>30.64718584144391</v>
+        <v>4.980167699234635</v>
       </c>
       <c r="E12" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F12" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>60.39259557499461</v>
+        <v>9.813796780936624</v>
       </c>
       <c r="D13" t="n">
-        <v>35.66548360777485</v>
+        <v>5.795641086263412</v>
       </c>
       <c r="E13" t="n">
-        <v>11.56798157524192</v>
+        <v>1.879797005976812</v>
       </c>
       <c r="F13" t="n">
-        <v>16.45797616671993</v>
+        <v>2.674421127091988</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
